--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventorySemiProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventorySemiProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -33,13 +33,7 @@
     <t>Block</t>
   </si>
   <si>
-    <t>Tổng Block</t>
-  </si>
-  <si>
     <t>Hàng NG</t>
-  </si>
-  <si>
-    <t>Tổng Block OK</t>
   </si>
 </sst>
 </file>
@@ -394,20 +388,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="3" customWidth="1"/>
     <col min="2" max="2" width="24" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="3"/>
+    <col min="5" max="5" width="17.28515625" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,14 +412,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventorySemiProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventorySemiProductTemplate.xlsx
@@ -21,12 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Tên sản phẩm</t>
-  </si>
-  <si>
-    <t>Lô nguyên liệu</t>
-  </si>
-  <si>
     <t>SET</t>
   </si>
   <si>
@@ -34,6 +28,12 @@
   </si>
   <si>
     <t>Hàng NG</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm KC</t>
+  </si>
+  <si>
+    <t>Số lô tấm nguyên liệu</t>
   </si>
 </sst>
 </file>
@@ -401,19 +401,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
